--- a/data/source/2026-09-28/BSR_IT_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
+++ b/data/source/2026-09-28/BSR_IT_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="142">
   <si>
     <t>#</t>
   </si>
@@ -232,40 +232,187 @@
     <t>B0G66L48KD</t>
   </si>
   <si>
-    <t>https://www.amazon.itundefined</t>
-  </si>
-  <si>
-    <t>Bosch Aspiratore solidi-liquidi PAS20-220P (Tubi di prolunga, tubo di aspirazione 2,2 m, tubo a gomito/impugnatura, bocchette</t>
+    <t>Taglia: 20L - 1200W</t>
+  </si>
+  <si>
+    <t>Marchio: Bosch | Fonte di alimentazione: ac_dc | Tensione: 240 Volt | Componenti inclusi: Dotazione: PAS20-220, 2 tubi di prolunga (plastica), 1 tubo di aspirazione (2,2 m), 1 tubo a gomito/impugnatura, 1 bocchetta per pavimenti, 1 bocchetta per fessure, 1 borsa in tessuto (Uni), 1 filtro plissettato piatto, 1 UniversalAdapter | È cordless?: No</t>
+  </si>
+  <si>
+    <t>Bosch</t>
+  </si>
+  <si>
+    <t>https://www.amazon.it/stores/BoschDIY/page/C0E50987-D148-4E3F-80C4-79212A89392F?lp_asin=B0G66L48KD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Bosch Aspiratore solidi-liquidi PAS20-220P (Tubi di prolunga, tubo di aspirazione 2,2 m, tubo a gomito/impugnatura, bocchette, borsa in tessuto (Uni), filtro plissettato piatto, UniversalAdapter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motore da 1.200 W con potenza di aspirazione di 220 mbar: rimuove senza sforzo lo sporco umido e secco
+Filtro pieghettato piatto: per aspirare liquidi e residui secchi senza cambiare il filtro
+Funzione di soffiaggio: rimuove lo sporco dalle zone difficilmente accessibili
+Movimento facile e stabile: con contenitore da 20 l e ruote antiribaltamento
+Dotazione: PAS20-220, 2 tubi di prolunga (plastica), 1 tubo di aspirazione (2,2 m), 1 tubo a gomito/impugnatura, 1 bocchetta per pavimenti, 1 bocchetta per fessure, 1 borsa in tessuto (Uni), 1 filtro plissettato piatto, 1 UniversalAdapter</t>
   </si>
   <si>
     <t>https://www.amazon.it/dp/B0G66L48KD?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/613TijBpXcL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/416etd8+eUL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H6MY3KH1</t>
+  </si>
+  <si>
+    <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspiratori solidi-liquidi per uso domestico</t>
+  </si>
+  <si>
+    <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+  </si>
+  <si>
+    <t>Aspiratori solidi-liquidi per uso domestico</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>AMZ</t>
+  </si>
+  <si>
+    <t>12天</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>6 Chilogrammi</t>
+  </si>
+  <si>
+    <t>37,6L x 36,5l x 49,2H cm</t>
+  </si>
+  <si>
+    <t>9.89 kg</t>
+  </si>
+  <si>
+    <t>51.5 x 39.8 x 38.5 cm</t>
+  </si>
+  <si>
+    <t>51.50 x 39.80 x 38.50 cm</t>
+  </si>
+  <si>
+    <t>轻型标准大件</t>
   </si>
   <si>
     <t>B0FPMB88DH</t>
   </si>
   <si>
-    <t>EUREKA FloorShine 460 Lavapavimenti Senza Fili, Design Piatto 180° 11,5cm, Aspirazione 17000Pa 80% Recupero Acqua, Anti-Grovi</t>
+    <t>Colore: Floorshine 460 Nero</t>
+  </si>
+  <si>
+    <t>Marchio: EUREKA | Caratteristica speciale: Alta potenza, Bagnato/asciutto, Leggero, Potente aspirazione | Tipo di filtro: Schiuma | Superfici consigliate: Tutti i tipi di pavimento | Fonte di alimentazione: A batteria</t>
+  </si>
+  <si>
+    <t>EUREKA</t>
+  </si>
+  <si>
+    <t>https://www.amazon.it/stores/Eureka/page/18550E79-9244-471B-AFC2-A01E35368E02?lp_asin=B0FPMB88DH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>EUREKA FloorShine 460 Lavapavimenti Senza Fili, Design Piatto 180° 11,5cm, Aspirazione 17000Pa 80% Recupero Acqua, Anti-Groviglio Pro, Pulizia Bordi, Auto-Asciugatura, Leggero 3,93kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Ultra-Piatto Inclinazione 180° per Pulizia Totale: Il design innovativo inclinazione 180° di FloorShine NEW460 con altezza di soli 8,8 cm nella posizione di riposo permette di pulire facilmente sotto mobili bassi come divani e letti, aree tradizionalmente difficili da raggiungere. Il sistema di canalizzazione dell'acqua impedisce il riflusso del liquido sporco, garantendo una pulizia igienica e continua senza interruzioni. Ideale per ambienti moderni con arredamento minimalista, questa caratteristica assicura che nessuna zona della casa venga trascurata, offrendo risultati impeccabili con il minimo sforzo.
+Autoasciugatura Igienizzante: Grazie al sistema di autoasciugatura ad aria calda ad alta temperatura, la lavapavimenti senza filo FloorShine NEW460 mantiene il rullo asciutto e igienizzato dopo ogni utilizzo, prevenendo la formazione di muffe e cattivi odori. Il flusso d'aria ad alta velocità asciuga completamente le spazzole in pochi minuti, eliminando la necessità di interventi manuali. Questa funzione è particolarmente vantaggiosa per famiglie con bambini o animali domestici, assicurando un ambiente sempre fresco e sanitizzato senza ulteriore manutenzione.
+Pulizia 4-in-1 con Aspirazione Potente 17.000 Pa: L'aspirapolvere e lavapavimenti FloorShine 460 combina 4 fasi di pulizia in un unico gesto: spruzzo uniforme dell'acqua, lavaggio con spazzola ad alta velocità (495 giri/min), raschiatura efficiente e aspirazione potente con recupero del 90% dell'acqua. La tecnologia "Spruzza-Lava-Raschia-Ricicla" garantisce pavimenti asciutti e pronti per essere calpestati immediatamente, mentre l'aspirazione integrata gestisce simultaneamente liquidi e solidi. Perfetto per sostanze difficili come peli di animali o residui alimentari.
+Maneggevolezza Avanzata e Design Ergonomico: Con un peso ridotto e un sistema di propulsione automatica che allevia lo sforzo dell'utente, FloorShine 460 offre una manovrabilità eccezionale grazie alle ruote multi-direzionali e all'impugnatura ergonomica. La pressione sul pavimento di 34 N assicura una pulizia profonda senza sforzo fisico, mentre l'inclinazione del dispositivo attiva automaticamente la modalità pausa. Il design compatto e la batteria da 30 minuti lo rendono ideale per pulizie estese senza interruzioni.
+Doppia Modalità e Serbatoi ad Alta Capacità 600 ml: La doppia modalità di pulizia (Normale e Asciutta) si adatta a ogni scenario: dalla pulizia quotidiana alla gestione di liquidi abbondanti in bagno o cucina. I serbatoi da 600 ml (acqua pulita e sporca) offrono il 50% di autonomia in più rispetto ai modelli precedenti, riducendo la frequenza di ricarica. La base di ricarica integrata e gli avvisi vocali completano un'esperienza d'uso intuitiva e senza complicazioni.</t>
   </si>
   <si>
     <t>https://www.amazon.it/dp/B0FPMB88DH?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71Veas8E33L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31jc+Ze-lQL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H3NV8G7Q</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2025-10-12</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>3,93 Chilogrammi</t>
+  </si>
+  <si>
+    <t>20L x 21,8l x 110,2H cm</t>
+  </si>
+  <si>
+    <t>7.51 kg</t>
+  </si>
+  <si>
+    <t>76 x 31.6 x 26.8 cm</t>
+  </si>
+  <si>
+    <t>76.00 x 31.60 x 26.80 cm</t>
   </si>
   <si>
     <t>B0G7GJZ7WQ</t>
   </si>
   <si>
-    <t>JONR 20000 Pa H2 aspirapolvere a secco bagnato,Design Innovativo Protezione Odori,Serbatoio Acqua Extra Grande 1500ml con Pos</t>
+    <t>Marchio: JONR | Caratteristica speciale: Duo-Clean | Tipo di filtro: Sistema di filtrazione multistadio | Superfici consigliate: Tutti i tipi di pavimento | Fonte di alimentazione: A batteria</t>
+  </si>
+  <si>
+    <t>JONR</t>
+  </si>
+  <si>
+    <t>https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>JONR 20000 Pa H2 aspirapolvere a secco bagnato,Design Innovativo Protezione Odori,Serbatoio Acqua Extra Grande 1500ml con Posizione Piatta a 180° (Potenza Aspirazione e Acqua Inalterate),45 Min. (S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.000 Pa di potente aspirazione e doppie spazzole laterali assicurano una copertura completa da bordo a bordo, il rullo ad alta velocità da 500 RPM e lo spazzolamento pressorizzato sollevano facilmente lo sporco ostinato.
+Leader Leggero del Mercato, Guida Tu - 3.5kg / 7.7lb Il punto di riferimento del settore consente una facile operazione con una mano senza ingombro. Pulizia con trazione auto-drive, senza sforzo come una passeggiata, assemblaggio/smontaggio in 3 secondi per una manutenzione senza attrezzi e senza mani
+Prestazioni leader della batteria, pulisce tutta la casa in un unico passaggio - 45 minuti di pulizia potente puliscono grandi spazi dall'inizio alla fine senza ricarica. Il serbatoio dell'acqua pulita da 50,7 Fl oz / 1500 ml consente una pulizia dell'intera casa con acqua fresca. La base di ricarica salvaspazio inizia a caricare immediatamente al momento della connessione
+Trattenere rifiuti solidi e liquidi, prevenendo odori e crescita fungina - Il filtro monouso e biodegradabile trattiene le macchie liquide, eliminando le preoccupazioni per i residui che si attaccano alle pareti, il serbatoio dell'acqua sporca da 650 ml montato sul fondo isola i rifiuti, previene il riflusso e contiene gli odori, il motore impermeabile con classificazione IPX6 e la pulizia diretta dell'acqua del rullo fermano gli odori e i funghi — un must per i proprietari di animali domestici
+Totalmente piatto a 180° - Posizione completamente piatta a 180°, mantenendo la piena potenza di aspirazione per scivolare sotto i mobili e affrontare aree difficili da raggiungere e basse.</t>
   </si>
   <si>
     <t>https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>3,5 Chilogrammi</t>
+  </si>
+  <si>
+    <t>27L x 21l x 110H cm</t>
+  </si>
+  <si>
+    <t>6.78 kg</t>
+  </si>
+  <si>
+    <t>61 x 33.8 x 32.3 cm</t>
+  </si>
+  <si>
+    <t>61.00 x 33.80 x 32.30 cm</t>
   </si>
   <si>
     <t>导出时自动对相同ASIN去重。可能导致导出的产品总数与页面显示数量不一致</t>
@@ -283,13 +430,7 @@
     <t>市场份额</t>
   </si>
   <si>
-    <t>未知品牌</t>
-  </si>
-  <si>
     <t>卖家</t>
-  </si>
-  <si>
-    <t>未知卖家</t>
   </si>
   <si>
     <t>卖家精灵官网：https://www.sellersprite.com</t>
@@ -455,11 +596,11 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -525,13 +666,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -569,13 +710,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -593,6 +734,50 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="undefined">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>192000</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>428799</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>270000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1246,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1257,56 +1442,61 @@
         <v>71</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O2" s="15">
+        <v>36936</v>
+      </c>
+      <c r="P2" s="15">
+        <v>95511</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>0.74</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>70</v>
+        <v>84</v>
+      </c>
+      <c r="T2" s="15">
+        <v>20</v>
       </c>
       <c r="U2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="V2" s="15" t="s">
-        <v>70</v>
+      <c r="V2" s="15">
+        <v>3300</v>
       </c>
       <c r="W2" s="15" t="s">
         <v>70</v>
@@ -1314,33 +1504,62 @@
       <c r="X2" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="19">
+      <c r="Y2" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="20">
         <v>147.46</v>
       </c>
-      <c r="AD2" s="20">
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="19">
         <v>38</v>
+      </c>
+      <c r="AE2" s="15">
+        <v>1</v>
       </c>
       <c r="AF2" s="21">
         <v>4.7</v>
       </c>
       <c r="AG2" s="22">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="AH2" s="20">
+        <v>10.91</v>
       </c>
       <c r="AI2" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="20" t="s">
-        <v>70</v>
+        <v>0.78</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL2" s="19">
+        <v>250</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="AN2" s="13" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="AO2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ2" s="20" t="s">
-        <v>70</v>
+      <c r="AP2" s="20">
+        <v>122.12</v>
+      </c>
+      <c r="AQ2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR2" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>70</v>
@@ -1367,7 +1586,7 @@
         <v>70</v>
       </c>
       <c r="BC2" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD2" s="13" t="s">
         <v>70</v>
@@ -1384,20 +1603,35 @@
       <c r="BH2" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ2" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="BK2" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL2" s="23" t="s">
+        <v>91</v>
+      </c>
       <c r="BM2" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN2" s="23" t="s">
+        <v>92</v>
+      </c>
       <c r="BO2" s="23" t="s">
-        <v>70</v>
+        <v>92</v>
+      </c>
+      <c r="BP2" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="BQ2" s="23" t="s">
-        <v>70</v>
+        <v>94</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1405,59 +1639,64 @@
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>70</v>
+        <v>98</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="1"/>
+        <v>105</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O3" s="15">
+        <v>63020</v>
+      </c>
+      <c r="P3" s="15">
+        <v>22927</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>0.4</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>70</v>
+        <v>106</v>
+      </c>
+      <c r="T3" s="15">
+        <v>84</v>
+      </c>
+      <c r="U3" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="V3" s="15">
+        <v>14279</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>70</v>
@@ -1465,11 +1704,20 @@
       <c r="X3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z3" s="19">
-        <v>139.34</v>
-      </c>
-      <c r="AD3" s="20">
+      <c r="Y3" s="19">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>169.99</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="19">
         <v>105</v>
+      </c>
+      <c r="AE3" s="15">
+        <v>0</v>
       </c>
       <c r="AF3" s="21">
         <v>3.9</v>
@@ -1477,12 +1725,20 @@
       <c r="AG3" s="22">
         <v>0</v>
       </c>
+      <c r="AH3" s="20">
+        <v>10.56</v>
+      </c>
       <c r="AI3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="20" t="s">
-        <v>70</v>
+        <v>0.79</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>351</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>70</v>
@@ -1490,8 +1746,18 @@
       <c r="AO3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ3" s="20" t="s">
-        <v>70</v>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>70</v>
@@ -1518,16 +1784,16 @@
         <v>70</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG3" s="13" t="s">
         <v>70</v>
@@ -1535,20 +1801,35 @@
       <c r="BH3" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ3" s="23" t="s">
+        <v>109</v>
+      </c>
       <c r="BK3" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL3" s="23" t="s">
+        <v>110</v>
+      </c>
       <c r="BM3" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN3" s="23" t="s">
+        <v>111</v>
+      </c>
       <c r="BO3" s="23" t="s">
-        <v>70</v>
+        <v>111</v>
+      </c>
+      <c r="BP3" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="BQ3" s="23" t="s">
-        <v>70</v>
+        <v>113</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1556,50 +1837,53 @@
         <v>70</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="H4" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="O4" s="15">
+        <v>912273</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="16">
+        <v>0</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="S4" s="18" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="T4" s="15" t="s">
         <v>70</v>
@@ -1616,9 +1900,20 @@
       <c r="X4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AD4" s="20">
+      <c r="Y4" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>298.41</v>
+      </c>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="19">
         <v>49</v>
+      </c>
+      <c r="AE4" s="15">
+        <v>0</v>
       </c>
       <c r="AF4" s="21">
         <v>3.5</v>
@@ -1626,12 +1921,20 @@
       <c r="AG4" s="22">
         <v>0</v>
       </c>
+      <c r="AH4" s="20">
+        <v>10.56</v>
+      </c>
       <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="20" t="s">
-        <v>70</v>
+        <v>0.81</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>193</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN4" s="13" t="s">
         <v>70</v>
@@ -1639,8 +1942,18 @@
       <c r="AO4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ4" s="20" t="s">
-        <v>70</v>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR4" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU4" s="13" t="s">
         <v>70</v>
@@ -1667,10 +1980,10 @@
         <v>70</v>
       </c>
       <c r="BC4" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD4" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE4" s="13" t="s">
         <v>70</v>
@@ -1684,23 +1997,38 @@
       <c r="BH4" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ4" s="23" t="s">
+        <v>124</v>
+      </c>
       <c r="BK4" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL4" s="23" t="s">
+        <v>125</v>
+      </c>
       <c r="BM4" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN4" s="23" t="s">
+        <v>126</v>
+      </c>
       <c r="BO4" s="23" t="s">
-        <v>70</v>
+        <v>126</v>
+      </c>
+      <c r="BP4" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="BQ4" s="23" t="s">
-        <v>70</v>
+        <v>128</v>
+      </c>
+      <c r="BR4" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
@@ -1774,30 +2102,36 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.it/dp/B0G66L48KD"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.it/stores/BoschDIY/page/C0E50987-D148-4E3F-80C4-79212A89392F?lp_asin=B0G66L48KD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.it/dp/B0G66L48KD?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/613TijBpXcL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B0G66L48KD"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.it/dp/B0FPMB88DH"/>
-    <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0FPMB88DH?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Veas8E33L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0FPMB88DH"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://m.media-amazon.com/images/I/416etd8+eUL._AC_US600_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B0H6MY3KH1"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.it/b?node=218944968031"/>
+    <hyperlink ref="N2" r:id="rId7"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0FPMB88DH"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.it/stores/Eureka/page/18550E79-9244-471B-AFC2-A01E35368E02?lp_asin=B0FPMB88DH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0FPMB88DH?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/31jc+Ze-lQL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.it/dp/B0H3NV8G7Q"/>
+    <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.it/b?node=218944968031"/>
+    <hyperlink ref="N3" r:id="rId14"/>
+    <hyperlink ref="C4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="G4" r:id="rId16" tooltip="https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J4" r:id="rId17" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1"/>
+    <hyperlink ref="K4" r:id="rId18" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg"/>
+    <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.it/b?node=218944968031"/>
+    <hyperlink ref="N4" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -1817,38 +2151,84 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B2" s="15">
+        <v>84</v>
+      </c>
+      <c r="C2" s="15">
+        <v>14279</v>
+      </c>
+      <c r="D2" s="15">
+        <v>5731</v>
+      </c>
+      <c r="E2" s="15">
+        <v>974213</v>
+      </c>
+      <c r="F2" s="20">
+        <v>169.99</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.8077</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="15">
+        <v>20</v>
+      </c>
+      <c r="C3" s="15">
+        <v>2949</v>
+      </c>
+      <c r="D3" s="15">
+        <v>74</v>
+      </c>
+      <c r="E3" s="15">
+        <v>10912</v>
+      </c>
+      <c r="F3" s="20">
+        <v>147.46</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.1923</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="15">
         <v>0</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C4" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D4" s="15">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E4" s="15">
         <v>0</v>
       </c>
-      <c r="F2" s="19">
-        <v>95.6</v>
-      </c>
-      <c r="G2" s="22">
+      <c r="F4" s="20">
+        <v>298.41</v>
+      </c>
+      <c r="G4" s="22">
         <v>0</v>
       </c>
     </row>
@@ -1871,7 +2251,7 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>19</v>
@@ -1880,39 +2260,39 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B2" s="15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="C2" s="15">
-        <v>0</v>
+        <v>21350</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>5805</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>95.6</v>
+        <v>1191689</v>
+      </c>
+      <c r="F2" s="20">
+        <v>205.29</v>
       </c>
       <c r="G2" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1931,37 +2311,37 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:1" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
